--- a/jpcore-r4b/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -278,8 +278,8 @@
     <t>診断のための検査、治療、手術などのサービスリクエストの記録</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 / A resource should have narrative for robust management {text.`div`.exists()}prr-1:コードが存在する場合に限り、注文詳細は存在するものとします。 / orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -307,13 +307,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -326,26 +326,26 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
     <t>ServiceRequest.meta.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -365,13 +365,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -387,20 +387,20 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ServiceRequest.meta.versionId</t>
   </si>
   <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi) / Version specific identifier</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。 / The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。 / The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
   </si>
   <si>
     <t>Meta.versionId</t>
@@ -413,13 +413,13 @@
 </t>
   </si>
   <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
+    <t>リソースのバージョンが最後に変更されたとき / When the resource version last changed</t>
+  </si>
+  <si>
+    <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。 / When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>この値はリソースが初めて作成される場合を除いて常に設定されています。サーバー/リソースマネージャーがこの値を設定します。クライアントが提供する値は関係ありません。これはHTTP Last-Modifiedに相当し、[read](http://hl7.org/fhir/R4B/http.html#read)のインタラクションで同じ値を持つべきです。 / This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
   </si>
   <si>
     <t>Meta.lastUpdated</t>
@@ -432,13 +432,14 @@
 </t>
   </si>
   <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+    <t>リソースがどこから来たかを特定する / Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。 / A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。 / In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
 This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
   </si>
   <si>
@@ -452,13 +453,13 @@
 </t>
   </si>
   <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+    <t>このリソースが適合を主張するプロファイル / Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>このリソースが準拠すると主張する [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) リソースに関するプロファイルのリストです。URL は [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url) への参照です。 / A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>これらの主張が時間の経過に伴って検証または更新される方法と、それらを決定するサーバーや他の基盤に任されます。プロファイルURLのリストは1セットです。 / It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
     <t>Meta.profile</t>
@@ -471,13 +472,13 @@
 </t>
   </si>
   <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたセキュリティラベル / Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースにはセキュリティラベルが適用されています。これらのタグにより、特定のリソースが全体的なセキュリティポリシーやインフラストラクチャに関連付けられます。 / Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>セキュリティラベルは変更せずにリソースのバージョンを更新可能です。セキュリティラベルのリストはセットであり、一意性はシステム/コードに基づき、バージョンと表示は無視されます。 / The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -492,13 +493,13 @@
     <t>ServiceRequest.meta.tag</t>
   </si>
   <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたタグ / Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースに適用されるタグです。タグは、リソースをプロセスやワークフローに識別し、関連付けるために使用することが意図されており、アプリケーションはリソースの意味を解釈する際にタグを考慮する必要はありません。 / Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。 / The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>example</t>
@@ -513,13 +514,13 @@
     <t>ServiceRequest.implicitRules</t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -532,19 +533,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>人間の言語。 / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -564,13 +565,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト要約 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -590,19 +591,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>含まれている、インラインのリソース / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -612,7 +613,7 @@
     <t>ServiceRequest.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -621,14 +622,14 @@
     <t>ServiceRequest.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張により、安全に無視できない拡張を、安全に無視できる大多数の拡張と明確に区別することができます。これにより、実装者が拡張の存在を禁止する必要がなくなり、相互運用性が促進されます。詳細については、[修飾子拡張の定義](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension)を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -745,7 +746,7 @@
     <t>完了または終了したService Requestリソースの代替（への参照）</t>
   </si>
   <si>
-    <t>The request takes the place of the referenced completed or terminated request(s).</t>
+    <t>そのリクエストは、参照された完了または終了したリクエストの代わりを占めます。 / The request takes the place of the referenced completed or terminated request(s).</t>
   </si>
   <si>
     <t>Request.replaces</t>
@@ -773,7 +774,7 @@
     <t>サービスリクエストは、basedOn要素、このrequisition要素によって関係付けられる。同じrequisition要素の一部であるサービスリクエストは、初めに作成された後にその状態と管理が変化する視点から、一般的に独立して扱われる。</t>
   </si>
   <si>
-    <t>Some business processes need to know if multiple items were ordered as part of the same "requisition" for billing or other purposes.</t>
+    <t>一部のビジネスプロセスは、請求やその他の目的のために複数の項目が同じ「依頼」の一部として注文されたかどうかを知る必要がある。 / Some business processes need to know if multiple items were ordered as part of the same "requisition" for billing or other purposes.</t>
   </si>
   <si>
     <t>Request.groupIdentifier</t>
@@ -800,7 +801,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>The status of a service order.</t>
+    <t>サービスオーダーのステータス。 / The status of a service order.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-status|4.3.0</t>
@@ -833,7 +834,7 @@
     <t>この要素は、リソースが実際に適用されるタイミングや方法を意図的に変更するため、修飾子と表現される。</t>
   </si>
   <si>
-    <t>The kind of service request.</t>
+    <t>サービスのリクエストの種類 / The kind of service request.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-intent|4.3.0</t>
@@ -864,10 +865,10 @@
     <t>リソースを検索または表示するためのコンテキストまたはユースケースに応じて、複数の分類軸が存在する場合がある。粒度のレベルは、Value Setのカテゴリー概念によって定義される。</t>
   </si>
   <si>
-    <t>Used for filtering what service request are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Classification of the requested service.</t>
+    <t>取得および表示されるサービスリクエストのフィルタリングに使用される。 / Used for filtering what service request are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>要求されたサービスの分類。 / Classification of the requested service.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.3.0</t>
@@ -888,10 +889,10 @@
     <t>このサービスリクエストはどの程度早く対処されるべきかを示す。</t>
   </si>
   <si>
-    <t>If missing, this task should be performed with normal priority</t>
-  </si>
-  <si>
-    <t>Identifies the level of importance to be assigned to actioning the request.</t>
+    <t>欠落している場合、このタスクは通常の優先度で実行されるべきである / If missing, this task should be performed with normal priority</t>
+  </si>
+  <si>
+    <t>リクエストの対処に割り当てるべき重要度のレベルを特定する。 / Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
@@ -925,10 +926,10 @@
     <t>一般的には、コードと時間枠のみであるが、時には体の部位や実施者などの修飾語を追加して、禁止範囲を狭められる。code要素とdoNotPerform要素がともに否定を含む場合、禁止を強化することになり、二重否定解釈をしてはならない。</t>
   </si>
   <si>
-    <t>Used for do not ambulate, do not elevate head of bed, do not flush NG tube, do not take blood pressure on a certain arm, etc.</t>
-  </si>
-  <si>
-    <t>If missing, the request is a positive request e.g. "do perform"</t>
+    <t>歩行禁止、ベッド頭部挙上禁止、NGチューブフラッシュ禁止、特定の腕での血圧測定禁止などに使用される。 / Used for do not ambulate, do not elevate head of bed, do not flush NG tube, do not take blood pressure on a certain arm, etc.</t>
+  </si>
+  <si>
+    <t>欠落している場合、リクエストは肯定的なリクエスト、すなわち「実行する」である / If missing, the request is a positive request e.g. "do perform"</t>
   </si>
   <si>
     <t>Request.doNotPerform</t>
@@ -953,7 +954,7 @@
     <t>多くの検査・放射線処置コードは、血清または血漿グルコース、胸部 X 線など、検体・器官系が検査オーダー名に埋め込まれている。検体は、検査コードとは別に記録されないかもしれない。</t>
   </si>
   <si>
-    <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred] and a valueset using LOINC Order codes is available.</t>
+    <t>指定された個人、組織、または医療サービスによって実施できるテストやサービスのコード。ラボの場合、LOINCが（preferred）[http://build.fhir.org/terminologies.html#preferred]であり、LOINCオーダーコードを使用した値セットが[こちら]（valueset-diagnostic-requests.html）で利用可能です。 / Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred] and a valueset using LOINC Order codes is available.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-code|4.3.0</t>
@@ -990,7 +991,7 @@
     <t>リクエストされたサービス提供の指示についての医療記録からの情報については、supportingInformation要素を使用。</t>
   </si>
   <si>
-    <t>Codified order entry details which are based on order context.</t>
+    <t>注文コンテキストに基づくコード化された注文詳細。 / Codified order entry details which are based on order context.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.3.0</t>
@@ -1019,7 +1020,7 @@
     <t>サービスリクエスト時に、項目とは別に数を指定する必要がある。</t>
   </si>
   <si>
-    <t>When ordering a service the number of service items may need to be specified separately from the the service item.</t>
+    <t>サービスを注文する際、サービス項目の数をサービス項目とは別に指定する必要がある場合がある。 / When ordering a service the number of service items may need to be specified separately from the the service item.</t>
   </si>
   <si>
     <t>.quantity</t>
@@ -1130,7 +1131,7 @@
     <t>CodeableConceptが存在する場合、そのサービスを行うための前提条件を示す。例えば、「痛み」、「再発時」など。</t>
   </si>
   <si>
-    <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
+    <t>手続きを実行する前に満たされる必要がある前提条件を示すコード化された概念。たとえば、「痛み」、「フレアアップ時」など。 / A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.3.0</t>
@@ -1225,7 +1226,7 @@
     <t>参加者の資格ではなく役割。タスクではなく、能力を記述。例えば、「調剤薬局」、「精神科医」、「院内紹介」など。</t>
   </si>
   <si>
-    <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
+    <t>初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。 / Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/action-participant-role</t>
@@ -1281,7 +1282,7 @@
     <t>実際に行為が行われるべき好ましい場所を、コード化またはフリーテキスト形式で記述。例：自宅や介護施設など。</t>
   </si>
   <si>
-    <t>A location type where services are delivered.</t>
+    <t>サービスが提供される場所タイプ。 / A location type where services are delivered.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
@@ -1318,7 +1319,7 @@
     <t>この要素は照会理由を表し、サービスがどのように実行されるか、あるいは全く実行されないかどうかを決定するために使用される。CTスキャンの例で示したように、データが自由記述の場合は、CodeableConcept.text要素を使用する。</t>
   </si>
   <si>
-    <t>SNOMED CT Condition/Problem/Diagnosis Codes</t>
+    <t>サービス調査の依頼理由を正当化する診断または問題コード。 / SNOMED CT Condition/Problem/Diagnosis Codes</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.3.0</t>
@@ -1450,10 +1451,10 @@
     <t>ServiceRequest.codeにあるコードに暗黙の了解がない場合にのみ使用する。使用例として、BodySiteをインラインコード化された要素ではなく、別のリソースとして扱う必要がある場合（例えば、別々に識別し追跡するため）、procedure.targetBodyStructureの拡張を使用してください。</t>
   </si>
   <si>
-    <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
-  </si>
-  <si>
-    <t>SNOMED CT Body site concepts</t>
+    <t>プロシージャがどこで実施されるかを知ることは、複数の部位が可能な場合の追跡に重要である。 / Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
+  </si>
+  <si>
+    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。 / SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
@@ -1868,7 +1869,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="201.8359375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="255.0" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="58.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
